--- a/src/conf/xlsx/column-and-parameter-descriptions-R5.xlsx
+++ b/src/conf/xlsx/column-and-parameter-descriptions-R5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\lhc-lx-ftdev04\sedinkinya\Projects\fhir-obs-viewer\src\conf\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DA2679-B96A-4178-99B6-4BA25A713C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91845FE0-28D5-499B-96E8-CFB0C10647BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6405" yWindow="2175" windowWidth="36585" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resources on LForms R5 server" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8736" uniqueCount="1627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8750" uniqueCount="1627">
   <si>
     <t>Legend</t>
   </si>
@@ -12333,7 +12333,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H1172"/>
+  <dimension ref="A1:H1174"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -32529,37 +32529,39 @@
       </c>
     </row>
     <row r="944" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A944" s="6"/>
-      <c r="B944" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="C944" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D944" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="E944" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F944" s="7" t="s">
+      <c r="A944" s="2"/>
+      <c r="B944" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C944" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D944" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E944" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F944" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G944" s="6"/>
-      <c r="H944" s="6" t="s">
-        <v>461</v>
+      <c r="G944" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H944" s="2" t="s">
+        <v>1626</v>
       </c>
     </row>
     <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" s="6"/>
       <c r="B945" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C945" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D945" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E945" s="6" t="s">
         <v>19</v>
@@ -32569,19 +32571,19 @@
       </c>
       <c r="G945" s="6"/>
       <c r="H945" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" s="6"/>
       <c r="B946" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C946" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D946" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E946" s="6" t="s">
         <v>19</v>
@@ -32591,19 +32593,19 @@
       </c>
       <c r="G946" s="6"/>
       <c r="H946" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A947" s="6"/>
       <c r="B947" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C947" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D947" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E947" s="6" t="s">
         <v>19</v>
@@ -32613,63 +32615,63 @@
       </c>
       <c r="G947" s="6"/>
       <c r="H947" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A948" s="6"/>
       <c r="B948" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C948" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D948" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E948" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F948" s="7" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G948" s="6"/>
       <c r="H948" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A949" s="6"/>
       <c r="B949" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C949" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D949" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E949" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F949" s="7" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G949" s="6"/>
       <c r="H949" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A950" s="6"/>
       <c r="B950" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C950" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D950" s="6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E950" s="6" t="s">
         <v>19</v>
@@ -32679,41 +32681,41 @@
       </c>
       <c r="G950" s="6"/>
       <c r="H950" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A951" s="6"/>
       <c r="B951" s="6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C951" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D951" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E951" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F951" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F951" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G951" s="6"/>
       <c r="H951" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" s="6"/>
       <c r="B952" s="6" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C952" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D952" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E952" s="6" t="s">
         <v>31</v>
@@ -32723,704 +32725,706 @@
       </c>
       <c r="G952" s="6"/>
       <c r="H952" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" s="6"/>
       <c r="B953" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C953" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D953" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E953" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F953" s="7" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="F953" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G953" s="6"/>
       <c r="H953" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" s="6"/>
       <c r="B954" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C954" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D954" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E954" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F954" s="7" t="s">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="G954" s="6"/>
       <c r="H954" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" s="6"/>
       <c r="B955" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C955" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D955" s="6" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E955" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F955" s="7" t="s">
-        <v>487</v>
+        <v>452</v>
       </c>
       <c r="G955" s="6"/>
       <c r="H955" s="6" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" s="6"/>
       <c r="B956" s="6" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C956" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D956" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E956" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F956" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G956" s="6"/>
       <c r="H956" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A957" s="6"/>
-      <c r="B957" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="C957" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D957" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="E957" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F957" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G957" s="6"/>
-      <c r="H957" s="6" t="s">
-        <v>493</v>
+      <c r="A957" s="2"/>
+      <c r="B957" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D957" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E957" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F957" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G957" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="H957" s="2" t="s">
+        <v>1624</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" s="6"/>
       <c r="B958" s="6" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C958" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D958" s="6" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E958" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F958" s="7" t="s">
-        <v>48</v>
+        <v>490</v>
       </c>
       <c r="G958" s="6"/>
       <c r="H958" s="6" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" s="6"/>
       <c r="B959" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C959" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D959" s="6" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E959" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F959" s="7" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="G959" s="6"/>
       <c r="H959" s="6" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" s="6"/>
       <c r="B960" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C960" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D960" s="6" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E960" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F960" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G960" s="6"/>
       <c r="H960" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" s="6"/>
       <c r="B961" s="6" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C961" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D961" s="6" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="E961" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F961" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G961" s="6"/>
       <c r="H961" s="6" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A962" s="6"/>
       <c r="B962" s="6" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C962" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D962" s="6" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E962" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F962" s="7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="G962" s="6"/>
       <c r="H962" s="6" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" s="6"/>
       <c r="B963" s="6" t="s">
-        <v>64</v>
+        <v>500</v>
       </c>
       <c r="C963" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D963" s="6" t="s">
-        <v>65</v>
+        <v>501</v>
       </c>
       <c r="E963" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F963" s="7" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G963" s="6"/>
-      <c r="H963" s="6"/>
+      <c r="H963" s="6" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" s="6"/>
       <c r="B964" s="6" t="s">
-        <v>66</v>
+        <v>503</v>
       </c>
       <c r="C964" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D964" s="6" t="s">
-        <v>66</v>
+        <v>503</v>
       </c>
       <c r="E964" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F964" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G964" s="6"/>
       <c r="H964" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" s="6"/>
       <c r="B965" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C965" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D965" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E965" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F965" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G965" s="6"/>
-      <c r="H965" s="6" t="s">
-        <v>506</v>
-      </c>
+      <c r="H965" s="6"/>
     </row>
     <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" s="6"/>
       <c r="B966" s="6" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="C966" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D966" s="6" t="s">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="E966" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F966" s="7" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G966" s="6"/>
       <c r="H966" s="6" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" s="6"/>
       <c r="B967" s="6" t="s">
-        <v>509</v>
+        <v>66</v>
       </c>
       <c r="C967" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D967" s="6" t="s">
-        <v>509</v>
+        <v>67</v>
       </c>
       <c r="E967" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F967" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G967" s="6"/>
       <c r="H967" s="6" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" s="6"/>
       <c r="B968" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C968" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D968" s="6" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E968" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F968" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F968" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G968" s="6"/>
       <c r="H968" s="6" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" s="6"/>
       <c r="B969" s="6" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C969" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D969" s="6" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E969" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F969" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G969" s="6"/>
       <c r="H969" s="6" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A970" s="6"/>
       <c r="B970" s="6" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="C970" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D970" s="6" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E970" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F970" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F970" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G970" s="6"/>
       <c r="H970" s="6" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" s="6"/>
       <c r="B971" s="6" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="C971" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D971" s="6" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E971" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F971" s="7" t="s">
-        <v>521</v>
+        <v>56</v>
       </c>
       <c r="G971" s="6"/>
       <c r="H971" s="6" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A972" s="6"/>
       <c r="B972" s="6" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="C972" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D972" s="6" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E972" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F972" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G972" s="6"/>
       <c r="H972" s="6" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A973" s="6"/>
       <c r="B973" s="6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C973" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D973" s="6" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E973" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F973" s="7" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="G973" s="6"/>
       <c r="H973" s="6" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A974" s="6"/>
       <c r="B974" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C974" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D974" s="6" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E974" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F974" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G974" s="6"/>
       <c r="H974" s="6" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" s="6"/>
       <c r="B975" s="6" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="C975" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D975" s="6" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E975" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F975" s="7" t="s">
-        <v>490</v>
+        <v>526</v>
       </c>
       <c r="G975" s="6"/>
       <c r="H975" s="6" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A976" s="6"/>
       <c r="B976" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C976" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D976" s="6" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E976" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F976" s="7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="G976" s="6"/>
       <c r="H976" s="6" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A977" s="6"/>
       <c r="B977" s="6" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C977" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D977" s="6" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E977" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F977" s="12" t="s">
-        <v>536</v>
+        <v>19</v>
+      </c>
+      <c r="F977" s="7" t="s">
+        <v>490</v>
       </c>
       <c r="G977" s="6"/>
       <c r="H977" s="6" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" s="6"/>
       <c r="B978" s="6" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C978" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D978" s="6" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="E978" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F978" s="7" t="s">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="G978" s="6"/>
       <c r="H978" s="6" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" s="6"/>
       <c r="B979" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C979" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D979" s="6" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="E979" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F979" s="7" t="s">
-        <v>490</v>
+        <v>31</v>
+      </c>
+      <c r="F979" s="12" t="s">
+        <v>536</v>
       </c>
       <c r="G979" s="6"/>
       <c r="H979" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="980" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A980" t="s">
-        <v>681</v>
+      <c r="A980" s="6"/>
+      <c r="B980" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="C980" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D980" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E980" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F980" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="G980" s="6"/>
+      <c r="H980" s="6" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" s="6"/>
       <c r="B981" s="6" t="s">
-        <v>127</v>
+        <v>538</v>
       </c>
       <c r="C981" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D981" s="6" t="s">
-        <v>127</v>
+        <v>540</v>
       </c>
       <c r="E981" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F981" s="7" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="G981" s="6"/>
       <c r="H981" s="6" t="s">
-        <v>1503</v>
+        <v>541</v>
       </c>
     </row>
     <row r="982" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A982" s="6"/>
-      <c r="B982" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C982" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D982" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E982" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F982" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G982" s="6"/>
-      <c r="H982" s="6" t="s">
-        <v>1503</v>
+      <c r="A982" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" s="6"/>
       <c r="B983" s="6" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="C983" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D983" s="6" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="E983" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F983" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G983" s="6"/>
       <c r="H983" s="6" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" s="6"/>
       <c r="B984" s="6" t="s">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="C984" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D984" s="6" t="s">
-        <v>39</v>
+        <v>130</v>
       </c>
       <c r="E984" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F984" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G984" s="6"/>
       <c r="H984" s="6" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A985" s="6"/>
       <c r="B985" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C985" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D985" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E985" s="6" t="s">
         <v>19</v>
@@ -33430,19 +33434,19 @@
       </c>
       <c r="G985" s="6"/>
       <c r="H985" s="6" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" s="6"/>
       <c r="B986" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C986" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D986" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="E986" s="6" t="s">
         <v>19</v>
@@ -33452,19 +33456,19 @@
       </c>
       <c r="G986" s="6"/>
       <c r="H986" s="6" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" s="6"/>
       <c r="B987" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C987" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D987" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E987" s="6" t="s">
         <v>19</v>
@@ -33474,129 +33478,129 @@
       </c>
       <c r="G987" s="6"/>
       <c r="H987" s="6" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" s="6"/>
       <c r="B988" s="6" t="s">
-        <v>1508</v>
+        <v>48</v>
       </c>
       <c r="C988" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D988" s="6" t="s">
-        <v>1509</v>
+        <v>48</v>
       </c>
       <c r="E988" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F988" s="7" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G988" s="6"/>
       <c r="H988" s="6" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" s="6"/>
       <c r="B989" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C989" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D989" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E989" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F989" s="7" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G989" s="6"/>
       <c r="H989" s="6" t="s">
-        <v>1511</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" s="6"/>
       <c r="B990" s="6" t="s">
-        <v>52</v>
+        <v>1508</v>
       </c>
       <c r="C990" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D990" s="6" t="s">
-        <v>52</v>
+        <v>1509</v>
       </c>
       <c r="E990" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F990" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G990" s="6"/>
       <c r="H990" s="6" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" s="6"/>
       <c r="B991" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C991" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D991" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E991" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F991" s="7" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G991" s="6"/>
       <c r="H991" s="6" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" s="6"/>
       <c r="B992" s="6" t="s">
-        <v>1513</v>
+        <v>52</v>
       </c>
       <c r="C992" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D992" s="6" t="s">
-        <v>1514</v>
+        <v>52</v>
       </c>
       <c r="E992" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F992" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F992" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G992" s="6"/>
       <c r="H992" s="6" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="993" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A993" s="6"/>
       <c r="B993" s="6" t="s">
-        <v>394</v>
+        <v>52</v>
       </c>
       <c r="C993" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D993" s="6" t="s">
-        <v>396</v>
+        <v>55</v>
       </c>
       <c r="E993" s="6" t="s">
         <v>19</v>
@@ -33606,155 +33610,155 @@
       </c>
       <c r="G993" s="6"/>
       <c r="H993" s="6" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" s="6"/>
       <c r="B994" s="6" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="C994" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D994" s="6" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="E994" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F994" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F994" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G994" s="6"/>
       <c r="H994" s="6" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" s="6"/>
       <c r="B995" s="6" t="s">
-        <v>64</v>
+        <v>394</v>
       </c>
       <c r="C995" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D995" s="6" t="s">
-        <v>65</v>
+        <v>396</v>
       </c>
       <c r="E995" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F995" s="7" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G995" s="6"/>
-      <c r="H995" s="6"/>
+      <c r="H995" s="6" t="s">
+        <v>1516</v>
+      </c>
     </row>
     <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" s="6"/>
       <c r="B996" s="6" t="s">
-        <v>66</v>
+        <v>1517</v>
       </c>
       <c r="C996" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D996" s="6" t="s">
-        <v>66</v>
+        <v>1518</v>
       </c>
       <c r="E996" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F996" s="7" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G996" s="6"/>
       <c r="H996" s="6" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="997" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A997" s="6"/>
       <c r="B997" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C997" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D997" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E997" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F997" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G997" s="6"/>
-      <c r="H997" s="6" t="s">
-        <v>1521</v>
-      </c>
+      <c r="H997" s="6"/>
     </row>
     <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" s="6"/>
       <c r="B998" s="6" t="s">
-        <v>778</v>
+        <v>66</v>
       </c>
       <c r="C998" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D998" s="6" t="s">
-        <v>778</v>
+        <v>66</v>
       </c>
       <c r="E998" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F998" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G998" s="6"/>
       <c r="H998" s="6" t="s">
-        <v>779</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="999" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A999" s="6"/>
       <c r="B999" s="6" t="s">
-        <v>780</v>
+        <v>66</v>
       </c>
       <c r="C999" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D999" s="6" t="s">
-        <v>780</v>
+        <v>67</v>
       </c>
       <c r="E999" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F999" s="7" t="s">
-        <v>366</v>
+        <v>67</v>
       </c>
       <c r="G999" s="6"/>
       <c r="H999" s="6" t="s">
-        <v>781</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" s="6"/>
       <c r="B1000" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C1000" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1000" s="6" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="E1000" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1000" s="7" t="s">
-        <v>784</v>
+        <v>53</v>
       </c>
       <c r="G1000" s="6"/>
       <c r="H1000" s="6" t="s">
@@ -33764,13 +33768,13 @@
     <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1001" s="6"/>
       <c r="B1001" s="6" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C1001" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1001" s="6" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="E1001" s="6" t="s">
         <v>19</v>
@@ -33786,365 +33790,365 @@
     <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" s="6"/>
       <c r="B1002" s="6" t="s">
-        <v>166</v>
+        <v>782</v>
       </c>
       <c r="C1002" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1002" s="6" t="s">
-        <v>166</v>
+        <v>783</v>
       </c>
       <c r="E1002" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1002" s="7" t="s">
-        <v>53</v>
+        <v>784</v>
       </c>
       <c r="G1002" s="6"/>
       <c r="H1002" s="6" t="s">
-        <v>1522</v>
+        <v>779</v>
       </c>
     </row>
     <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" s="6"/>
       <c r="B1003" s="6" t="s">
-        <v>166</v>
+        <v>785</v>
       </c>
       <c r="C1003" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1003" s="6" t="s">
-        <v>168</v>
+        <v>786</v>
       </c>
       <c r="E1003" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1003" s="7" t="s">
-        <v>56</v>
+        <v>366</v>
       </c>
       <c r="G1003" s="6"/>
       <c r="H1003" s="6" t="s">
-        <v>1522</v>
+        <v>781</v>
       </c>
     </row>
     <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" s="6"/>
       <c r="B1004" s="6" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="C1004" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>71</v>
+        <v>166</v>
       </c>
       <c r="E1004" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1004" s="12" t="s">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="F1004" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G1004" s="6"/>
       <c r="H1004" s="6" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1005" s="6"/>
       <c r="B1005" s="6" t="s">
-        <v>715</v>
+        <v>166</v>
       </c>
       <c r="C1005" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1005" s="6" t="s">
-        <v>716</v>
+        <v>168</v>
       </c>
       <c r="E1005" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1005" s="7" t="s">
-        <v>1524</v>
+        <v>56</v>
       </c>
       <c r="G1005" s="6"/>
       <c r="H1005" s="6" t="s">
-        <v>1511</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" s="6"/>
       <c r="B1006" s="6" t="s">
-        <v>718</v>
+        <v>70</v>
       </c>
       <c r="C1006" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1006" s="6" t="s">
-        <v>719</v>
+        <v>71</v>
       </c>
       <c r="E1006" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1006" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F1006" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="G1006" s="6"/>
       <c r="H1006" s="6" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1007" s="6"/>
       <c r="B1007" s="6" t="s">
-        <v>173</v>
+        <v>715</v>
       </c>
       <c r="C1007" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1007" s="6" t="s">
-        <v>173</v>
+        <v>716</v>
       </c>
       <c r="E1007" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1007" s="7" t="s">
-        <v>53</v>
+        <v>1524</v>
       </c>
       <c r="G1007" s="6"/>
       <c r="H1007" s="6" t="s">
-        <v>420</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" s="6"/>
       <c r="B1008" s="6" t="s">
-        <v>179</v>
+        <v>718</v>
       </c>
       <c r="C1008" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1008" s="6" t="s">
-        <v>180</v>
+        <v>719</v>
       </c>
       <c r="E1008" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1008" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G1008" s="6"/>
       <c r="H1008" s="6" t="s">
-        <v>420</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" s="6"/>
       <c r="B1009" s="6" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="C1009" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1009" s="6" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="E1009" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1009" s="7" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="G1009" s="6"/>
       <c r="H1009" s="6" t="s">
-        <v>1526</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1010" s="6"/>
       <c r="B1010" s="6" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="C1010" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1010" s="6" t="s">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="E1010" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1010" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1010" s="6"/>
       <c r="H1010" s="6" t="s">
-        <v>1527</v>
+        <v>420</v>
       </c>
     </row>
     <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" s="6"/>
       <c r="B1011" s="6" t="s">
-        <v>271</v>
+        <v>91</v>
       </c>
       <c r="C1011" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1011" s="6" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="E1011" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1011" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1011" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G1011" s="6"/>
       <c r="H1011" s="6" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" s="6"/>
       <c r="B1012" s="6" t="s">
-        <v>193</v>
+        <v>271</v>
       </c>
       <c r="C1012" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1012" s="6" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="E1012" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1012" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G1012" s="6"/>
       <c r="H1012" s="6" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" s="6"/>
       <c r="B1013" s="6" t="s">
-        <v>196</v>
+        <v>271</v>
       </c>
       <c r="C1013" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1013" s="6" t="s">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="E1013" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1013" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F1013" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1013" s="6"/>
       <c r="H1013" s="6" t="s">
-        <v>892</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" s="6"/>
       <c r="B1014" s="6" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C1014" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1014" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E1014" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1014" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1014" s="6"/>
       <c r="H1014" s="6" t="s">
-        <v>762</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1015" s="6"/>
       <c r="B1015" s="6" t="s">
-        <v>282</v>
+        <v>196</v>
       </c>
       <c r="C1015" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1015" s="6" t="s">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="E1015" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1015" s="7" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="G1015" s="6"/>
       <c r="H1015" s="6" t="s">
-        <v>1530</v>
+        <v>892</v>
       </c>
     </row>
     <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" s="6"/>
       <c r="B1016" s="6" t="s">
-        <v>727</v>
+        <v>198</v>
       </c>
       <c r="C1016" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1016" s="6" t="s">
-        <v>729</v>
+        <v>198</v>
       </c>
       <c r="E1016" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1016" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1016" s="6"/>
       <c r="H1016" s="6" t="s">
-        <v>1531</v>
+        <v>762</v>
       </c>
     </row>
     <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" s="6"/>
       <c r="B1017" s="6" t="s">
-        <v>1532</v>
+        <v>282</v>
       </c>
       <c r="C1017" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1017" s="6" t="s">
-        <v>1532</v>
+        <v>284</v>
       </c>
       <c r="E1017" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1017" s="7" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G1017" s="6"/>
       <c r="H1017" s="6" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" s="6"/>
       <c r="B1018" s="6" t="s">
-        <v>1532</v>
+        <v>727</v>
       </c>
       <c r="C1018" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1018" s="6" t="s">
-        <v>1534</v>
+        <v>729</v>
       </c>
       <c r="E1018" s="6" t="s">
         <v>19</v>
@@ -34154,288 +34158,288 @@
       </c>
       <c r="G1018" s="6"/>
       <c r="H1018" s="6" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" s="6"/>
       <c r="B1019" s="6" t="s">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="C1019" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1019" s="6" t="s">
-        <v>1459</v>
+        <v>1532</v>
       </c>
       <c r="E1019" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1019" s="7" t="s">
-        <v>1536</v>
+        <v>53</v>
       </c>
       <c r="G1019" s="6"/>
       <c r="H1019" s="6" t="s">
-        <v>1460</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1020" s="6"/>
       <c r="B1020" s="6" t="s">
-        <v>215</v>
+        <v>1532</v>
       </c>
       <c r="C1020" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1020" s="6" t="s">
-        <v>215</v>
+        <v>1534</v>
       </c>
       <c r="E1020" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1020" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G1020" s="6"/>
       <c r="H1020" s="6" t="s">
-        <v>911</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" s="6"/>
       <c r="B1021" s="6" t="s">
-        <v>215</v>
+        <v>1535</v>
       </c>
       <c r="C1021" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1021" s="6" t="s">
-        <v>217</v>
+        <v>1459</v>
       </c>
       <c r="E1021" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1021" s="7" t="s">
-        <v>48</v>
+        <v>1536</v>
       </c>
       <c r="G1021" s="6"/>
       <c r="H1021" s="6" t="s">
-        <v>911</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" s="6"/>
       <c r="B1022" s="6" t="s">
-        <v>912</v>
+        <v>215</v>
       </c>
       <c r="C1022" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1022" s="6" t="s">
-        <v>913</v>
+        <v>215</v>
       </c>
       <c r="E1022" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1022" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G1022" s="6"/>
       <c r="H1022" s="6" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" s="6"/>
       <c r="B1023" s="6" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="C1023" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1023" s="6" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="E1023" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1023" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G1023" s="6"/>
       <c r="H1023" s="6" t="s">
-        <v>1537</v>
+        <v>911</v>
       </c>
     </row>
     <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1024" s="6"/>
       <c r="B1024" s="6" t="s">
-        <v>108</v>
+        <v>912</v>
       </c>
       <c r="C1024" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1024" s="6" t="s">
-        <v>109</v>
+        <v>913</v>
       </c>
       <c r="E1024" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1024" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G1024" s="6"/>
       <c r="H1024" s="6" t="s">
-        <v>1538</v>
+        <v>914</v>
       </c>
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" s="6"/>
       <c r="B1025" s="6" t="s">
-        <v>743</v>
+        <v>108</v>
       </c>
       <c r="C1025" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1025" s="6" t="s">
-        <v>744</v>
+        <v>108</v>
       </c>
       <c r="E1025" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1025" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1025" s="6"/>
       <c r="H1025" s="6" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" s="6"/>
       <c r="B1026" s="6" t="s">
-        <v>1540</v>
+        <v>108</v>
       </c>
       <c r="C1026" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1026" s="6" t="s">
-        <v>1541</v>
+        <v>109</v>
       </c>
       <c r="E1026" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1026" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G1026" s="6"/>
       <c r="H1026" s="6" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1027" t="s">
-        <v>542</v>
+      <c r="A1027" s="6"/>
+      <c r="B1027" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="C1027" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1027" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="E1027" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1027" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1027" s="6"/>
+      <c r="H1027" s="6" t="s">
+        <v>1539</v>
       </c>
     </row>
     <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" s="6"/>
       <c r="B1028" s="6" t="s">
-        <v>543</v>
+        <v>1540</v>
       </c>
       <c r="C1028" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1028" s="6" t="s">
-        <v>544</v>
+        <v>1541</v>
       </c>
       <c r="E1028" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1028" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1028" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="G1028" s="6"/>
       <c r="H1028" s="6" t="s">
-        <v>545</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1029" s="6"/>
-      <c r="B1029" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="C1029" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1029" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="E1029" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1029" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1029" s="6"/>
-      <c r="H1029" s="6" t="s">
-        <v>547</v>
+      <c r="A1029" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" s="6"/>
       <c r="B1030" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C1030" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1030" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E1030" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1030" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F1030" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1030" s="6"/>
       <c r="H1030" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" s="6"/>
       <c r="B1031" s="6" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C1031" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1031" s="6" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E1031" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1031" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1031" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G1031" s="6"/>
       <c r="H1031" s="6" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" s="6"/>
       <c r="B1032" s="6" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C1032" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1032" s="6" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E1032" s="6" t="s">
         <v>19</v>
@@ -34445,633 +34449,633 @@
       </c>
       <c r="G1032" s="6"/>
       <c r="H1032" s="6" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1033" s="6"/>
       <c r="B1033" s="6" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C1033" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1033" s="6" t="s">
-        <v>16</v>
+        <v>550</v>
       </c>
       <c r="E1033" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1033" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F1033" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1033" s="6"/>
       <c r="H1033" s="6" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" s="6"/>
       <c r="B1034" s="6" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="C1034" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1034" s="6" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="E1034" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1034" s="7" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G1034" s="6"/>
       <c r="H1034" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" s="6"/>
       <c r="B1035" s="6" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="C1035" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1035" s="6" t="s">
-        <v>555</v>
+        <v>16</v>
       </c>
       <c r="E1035" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1035" s="7" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="G1035" s="6"/>
       <c r="H1035" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1036" s="6"/>
       <c r="B1036" s="6" t="s">
-        <v>557</v>
+        <v>23</v>
       </c>
       <c r="C1036" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1036" s="6" t="s">
-        <v>557</v>
+        <v>23</v>
       </c>
       <c r="E1036" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1036" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G1036" s="6"/>
       <c r="H1036" s="6" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1037" s="6"/>
       <c r="B1037" s="6" t="s">
-        <v>557</v>
+        <v>23</v>
       </c>
       <c r="C1037" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1037" s="6" t="s">
-        <v>15</v>
+        <v>555</v>
       </c>
       <c r="E1037" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1037" s="12" t="s">
-        <v>288</v>
+        <v>19</v>
+      </c>
+      <c r="F1037" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G1037" s="6"/>
       <c r="H1037" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1038" s="6"/>
       <c r="B1038" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C1038" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1038" s="6" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E1038" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1038" s="12" t="s">
-        <v>288</v>
+        <v>19</v>
+      </c>
+      <c r="F1038" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G1038" s="6"/>
       <c r="H1038" s="6" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1039" s="6"/>
       <c r="B1039" s="6" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C1039" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1039" s="6" t="s">
-        <v>562</v>
+        <v>15</v>
       </c>
       <c r="E1039" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1039" s="7" t="s">
-        <v>53</v>
+        <v>31</v>
+      </c>
+      <c r="F1039" s="12" t="s">
+        <v>288</v>
       </c>
       <c r="G1039" s="6"/>
       <c r="H1039" s="6" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1040" s="6"/>
       <c r="B1040" s="6" t="s">
-        <v>394</v>
+        <v>559</v>
       </c>
       <c r="C1040" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1040" s="6" t="s">
-        <v>396</v>
+        <v>560</v>
       </c>
       <c r="E1040" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1040" s="7" t="s">
-        <v>60</v>
+        <v>31</v>
+      </c>
+      <c r="F1040" s="12" t="s">
+        <v>288</v>
       </c>
       <c r="G1040" s="6"/>
       <c r="H1040" s="6" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1041" s="6"/>
       <c r="B1041" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C1041" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1041" s="6" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E1041" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1041" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G1041" s="6"/>
       <c r="H1041" s="6" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" s="6"/>
       <c r="B1042" s="6" t="s">
-        <v>567</v>
+        <v>394</v>
       </c>
       <c r="C1042" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1042" s="6" t="s">
-        <v>567</v>
+        <v>396</v>
       </c>
       <c r="E1042" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1042" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1042" s="6"/>
       <c r="H1042" s="6" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" s="6"/>
       <c r="B1043" s="6" t="s">
-        <v>64</v>
+        <v>565</v>
       </c>
       <c r="C1043" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1043" s="6" t="s">
-        <v>65</v>
+        <v>565</v>
       </c>
       <c r="E1043" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1043" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G1043" s="6"/>
-      <c r="H1043" s="6"/>
+      <c r="H1043" s="6" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" s="6"/>
       <c r="B1044" s="6" t="s">
-        <v>66</v>
+        <v>567</v>
       </c>
       <c r="C1044" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1044" s="6" t="s">
-        <v>66</v>
+        <v>567</v>
       </c>
       <c r="E1044" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1044" s="7" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G1044" s="6"/>
       <c r="H1044" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" s="6"/>
       <c r="B1045" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1045" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1045" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E1045" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1045" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G1045" s="6"/>
-      <c r="H1045" s="6" t="s">
-        <v>569</v>
-      </c>
+      <c r="H1045" s="6"/>
     </row>
     <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" s="6"/>
       <c r="B1046" s="6" t="s">
-        <v>570</v>
+        <v>66</v>
       </c>
       <c r="C1046" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1046" s="6" t="s">
-        <v>570</v>
+        <v>66</v>
       </c>
       <c r="E1046" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1046" s="7" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G1046" s="6"/>
       <c r="H1046" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1047" s="6"/>
       <c r="B1047" s="6" t="s">
-        <v>570</v>
+        <v>66</v>
       </c>
       <c r="C1047" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1047" s="6" t="s">
-        <v>572</v>
+        <v>67</v>
       </c>
       <c r="E1047" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1047" s="7" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G1047" s="6"/>
       <c r="H1047" s="6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" s="6"/>
       <c r="B1048" s="6" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C1048" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1048" s="6" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E1048" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1048" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1048" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G1048" s="6"/>
       <c r="H1048" s="6" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" s="6"/>
       <c r="B1049" s="6" t="s">
-        <v>523</v>
+        <v>570</v>
       </c>
       <c r="C1049" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1049" s="6" t="s">
-        <v>523</v>
+        <v>572</v>
       </c>
       <c r="E1049" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1049" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G1049" s="6"/>
       <c r="H1049" s="6" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1050" s="6"/>
       <c r="B1050" s="6" t="s">
-        <v>523</v>
+        <v>573</v>
       </c>
       <c r="C1050" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1050" s="6" t="s">
-        <v>525</v>
+        <v>574</v>
       </c>
       <c r="E1050" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1050" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="F1050" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1050" s="6"/>
       <c r="H1050" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" s="6"/>
       <c r="B1051" s="6" t="s">
-        <v>70</v>
+        <v>523</v>
       </c>
       <c r="C1051" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1051" s="6" t="s">
-        <v>71</v>
+        <v>523</v>
       </c>
       <c r="E1051" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1051" s="12" t="s">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="F1051" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G1051" s="6"/>
       <c r="H1051" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="1052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1052" s="6"/>
       <c r="B1052" s="6" t="s">
-        <v>579</v>
+        <v>523</v>
       </c>
       <c r="C1052" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1052" s="6" t="s">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="E1052" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1052" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1052" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G1052" s="6"/>
       <c r="H1052" s="6" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
     </row>
     <row r="1053" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1053" s="6"/>
       <c r="B1053" s="6" t="s">
-        <v>582</v>
+        <v>70</v>
       </c>
       <c r="C1053" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1053" s="6" t="s">
-        <v>582</v>
+        <v>71</v>
       </c>
       <c r="E1053" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1053" s="7" t="s">
-        <v>26</v>
+        <v>31</v>
+      </c>
+      <c r="F1053" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="G1053" s="6"/>
       <c r="H1053" s="6" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="1054" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1054" s="6"/>
       <c r="B1054" s="6" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C1054" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1054" s="6" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="E1054" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1054" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
+      </c>
+      <c r="F1054" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1054" s="6"/>
       <c r="H1054" s="6" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1055" s="6"/>
       <c r="B1055" s="6" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="C1055" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1055" s="6" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="E1055" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1055" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1055" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="G1055" s="6"/>
       <c r="H1055" s="6" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1056" s="6"/>
       <c r="B1056" s="6" t="s">
-        <v>173</v>
+        <v>584</v>
       </c>
       <c r="C1056" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1056" s="6" t="s">
-        <v>173</v>
+        <v>584</v>
       </c>
       <c r="E1056" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1056" s="7" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G1056" s="6"/>
       <c r="H1056" s="6" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1057" s="6"/>
       <c r="B1057" s="6" t="s">
-        <v>179</v>
+        <v>586</v>
       </c>
       <c r="C1057" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1057" s="6" t="s">
-        <v>180</v>
+        <v>587</v>
       </c>
       <c r="E1057" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1057" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="F1057" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1057" s="6"/>
       <c r="H1057" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1058" s="6"/>
       <c r="B1058" s="6" t="s">
-        <v>590</v>
+        <v>173</v>
       </c>
       <c r="C1058" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1058" s="6" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="E1058" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1058" s="7" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="G1058" s="6"/>
       <c r="H1058" s="6" t="s">
-        <v>554</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1059" s="6"/>
       <c r="B1059" s="6" t="s">
-        <v>591</v>
+        <v>179</v>
       </c>
       <c r="C1059" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1059" s="6" t="s">
-        <v>591</v>
+        <v>180</v>
       </c>
       <c r="E1059" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1059" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G1059" s="6"/>
       <c r="H1059" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1060" s="6"/>
       <c r="B1060" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C1060" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1060" s="6" t="s">
-        <v>593</v>
+        <v>119</v>
       </c>
       <c r="E1060" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1060" s="7" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="G1060" s="6"/>
       <c r="H1060" s="6" t="s">
-        <v>594</v>
+        <v>554</v>
       </c>
     </row>
     <row r="1061" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1061" s="6"/>
       <c r="B1061" s="6" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C1061" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1061" s="6" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="E1061" s="6" t="s">
         <v>19</v>
@@ -35081,63 +35085,63 @@
       </c>
       <c r="G1061" s="6"/>
       <c r="H1061" s="6" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1062" s="6"/>
       <c r="B1062" s="6" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="C1062" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1062" s="6" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E1062" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1062" s="7" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="G1062" s="6"/>
       <c r="H1062" s="6" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1063" s="6"/>
       <c r="B1063" s="6" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C1063" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1063" s="6" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E1063" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1063" s="7" t="s">
-        <v>171</v>
+        <v>35</v>
       </c>
       <c r="G1063" s="6"/>
       <c r="H1063" s="6" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1064" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1064" s="6"/>
       <c r="B1064" s="6" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C1064" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1064" s="6" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E1064" s="6" t="s">
         <v>19</v>
@@ -35147,285 +35151,285 @@
       </c>
       <c r="G1064" s="6"/>
       <c r="H1064" s="6" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1065" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1065" s="6"/>
       <c r="B1065" s="6" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C1065" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1065" s="6" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E1065" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1065" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1065" s="7" t="s">
+        <v>171</v>
       </c>
       <c r="G1065" s="6"/>
       <c r="H1065" s="6" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1066" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1066" s="6"/>
       <c r="B1066" s="6" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C1066" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1066" s="6" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="E1066" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1066" s="7" t="s">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="G1066" s="6"/>
       <c r="H1066" s="6" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1067" s="6"/>
       <c r="B1067" s="6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C1067" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1067" s="6" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E1067" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1067" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="F1067" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1067" s="6"/>
       <c r="H1067" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1068" s="6"/>
       <c r="B1068" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C1068" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1068" s="6" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="E1068" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1068" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1068" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G1068" s="6"/>
       <c r="H1068" s="6" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1069" s="2"/>
-      <c r="B1069" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="C1069" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1069" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="E1069" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1069" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="G1069" s="2" t="s">
-        <v>1617</v>
-      </c>
-      <c r="H1069" s="2" t="s">
-        <v>1615</v>
+      <c r="A1069" s="6"/>
+      <c r="B1069" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="C1069" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1069" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="E1069" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1069" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1069" s="6"/>
+      <c r="H1069" s="6" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="1070" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1070" s="6"/>
       <c r="B1070" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C1070" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1070" s="6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E1070" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1070" s="7" t="s">
-        <v>614</v>
+        <v>31</v>
+      </c>
+      <c r="F1070" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1070" s="6"/>
       <c r="H1070" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="1071" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1071" s="6"/>
-      <c r="B1071" s="6" t="s">
-        <v>616</v>
-      </c>
-      <c r="C1071" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1071" s="6" t="s">
-        <v>616</v>
-      </c>
-      <c r="E1071" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1071" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="G1071" s="6"/>
-      <c r="H1071" s="6" t="s">
-        <v>617</v>
+      <c r="A1071" s="2"/>
+      <c r="B1071" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C1071" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1071" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E1071" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1071" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G1071" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H1071" s="2" t="s">
+        <v>1615</v>
       </c>
     </row>
     <row r="1072" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1072" s="6"/>
       <c r="B1072" s="6" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C1072" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1072" s="6" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="E1072" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1072" s="7" t="s">
-        <v>35</v>
+        <v>614</v>
       </c>
       <c r="G1072" s="6"/>
       <c r="H1072" s="6" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="1073" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1073" s="6"/>
       <c r="B1073" s="6" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C1073" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1073" s="6" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E1073" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1073" s="7" t="s">
-        <v>35</v>
+        <v>614</v>
       </c>
       <c r="G1073" s="6"/>
       <c r="H1073" s="6" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="1074" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1074" s="6"/>
       <c r="B1074" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C1074" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1074" s="6" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E1074" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1074" s="12" t="s">
-        <v>623</v>
+        <v>19</v>
+      </c>
+      <c r="F1074" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G1074" s="6"/>
       <c r="H1074" s="6" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1075" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1075" s="6"/>
       <c r="B1075" s="6" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C1075" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1075" s="6" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E1075" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1075" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G1075" s="6"/>
       <c r="H1075" s="6" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1076" s="6"/>
       <c r="B1076" s="6" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="C1076" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1076" s="6" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="E1076" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1076" s="7" t="s">
-        <v>53</v>
+        <v>31</v>
+      </c>
+      <c r="F1076" s="12" t="s">
+        <v>623</v>
       </c>
       <c r="G1076" s="6"/>
       <c r="H1076" s="6" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="1077" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1077" s="6"/>
       <c r="B1077" s="6" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C1077" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1077" s="6" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="E1077" s="6" t="s">
         <v>19</v>
@@ -35435,173 +35439,173 @@
       </c>
       <c r="G1077" s="6"/>
       <c r="H1077" s="6" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="1078" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1078" s="6"/>
       <c r="B1078" s="6" t="s">
-        <v>215</v>
+        <v>628</v>
       </c>
       <c r="C1078" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1078" s="6" t="s">
-        <v>215</v>
+        <v>628</v>
       </c>
       <c r="E1078" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1078" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G1078" s="6"/>
       <c r="H1078" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1079" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1079" s="6"/>
       <c r="B1079" s="6" t="s">
-        <v>215</v>
+        <v>628</v>
       </c>
       <c r="C1079" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1079" s="6" t="s">
-        <v>217</v>
+        <v>630</v>
       </c>
       <c r="E1079" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1079" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G1079" s="6"/>
       <c r="H1079" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1080" s="6"/>
       <c r="B1080" s="6" t="s">
-        <v>633</v>
+        <v>215</v>
       </c>
       <c r="C1080" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1080" s="6" t="s">
-        <v>633</v>
+        <v>215</v>
       </c>
       <c r="E1080" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1080" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G1080" s="6"/>
       <c r="H1080" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1081" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1081" s="6"/>
       <c r="B1081" s="6" t="s">
-        <v>635</v>
+        <v>215</v>
       </c>
       <c r="C1081" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1081" s="6" t="s">
-        <v>636</v>
+        <v>217</v>
       </c>
       <c r="E1081" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1081" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G1081" s="6"/>
       <c r="H1081" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="1082" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1082" s="6"/>
       <c r="B1082" s="6" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C1082" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1082" s="6" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E1082" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1082" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G1082" s="6"/>
       <c r="H1082" s="6" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1083" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1083" s="6"/>
       <c r="B1083" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C1083" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1083" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E1083" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1083" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G1083" s="6"/>
       <c r="H1083" s="6" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1084" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1084" s="6"/>
       <c r="B1084" s="6" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C1084" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1084" s="6" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="E1084" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1084" s="7" t="s">
-        <v>366</v>
+        <v>26</v>
       </c>
       <c r="G1084" s="6"/>
       <c r="H1084" s="6" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1085" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1085" s="6"/>
       <c r="B1085" s="6" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C1085" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1085" s="6" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E1085" s="6" t="s">
         <v>19</v>
@@ -35611,797 +35615,797 @@
       </c>
       <c r="G1085" s="6"/>
       <c r="H1085" s="6" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1086" s="6"/>
       <c r="B1086" s="6" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C1086" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1086" s="6" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E1086" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1086" s="7" t="s">
-        <v>35</v>
+        <v>366</v>
       </c>
       <c r="G1086" s="6"/>
       <c r="H1086" s="6" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1087" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1087" t="s">
-        <v>1543</v>
+      <c r="A1087" s="6"/>
+      <c r="B1087" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C1087" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1087" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="E1087" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1087" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1087" s="6"/>
+      <c r="H1087" s="6" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="1088" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1088" s="6"/>
       <c r="B1088" s="6" t="s">
-        <v>129</v>
+        <v>647</v>
       </c>
       <c r="C1088" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1088" s="6" t="s">
-        <v>130</v>
+        <v>648</v>
       </c>
       <c r="E1088" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1088" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G1088" s="6"/>
       <c r="H1088" s="6" t="s">
-        <v>1544</v>
+        <v>649</v>
       </c>
     </row>
     <row r="1089" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1089" s="6"/>
-      <c r="B1089" s="6" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C1089" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1089" s="6" t="s">
-        <v>1546</v>
-      </c>
-      <c r="E1089" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1089" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G1089" s="6"/>
-      <c r="H1089" s="6" t="s">
-        <v>1547</v>
+      <c r="A1089" t="s">
+        <v>1543</v>
       </c>
     </row>
     <row r="1090" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1090" s="6"/>
       <c r="B1090" s="6" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="C1090" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1090" s="6" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E1090" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1090" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G1090" s="6"/>
       <c r="H1090" s="6" t="s">
-        <v>1548</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1091" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1091" s="6"/>
       <c r="B1091" s="6" t="s">
-        <v>552</v>
+        <v>1545</v>
       </c>
       <c r="C1091" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1091" s="6" t="s">
-        <v>552</v>
+        <v>1546</v>
       </c>
       <c r="E1091" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1091" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1091" s="6"/>
       <c r="H1091" s="6" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1092" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1092" s="6"/>
       <c r="B1092" s="6" t="s">
-        <v>552</v>
+        <v>48</v>
       </c>
       <c r="C1092" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1092" s="6" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="E1092" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1092" s="7" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="G1092" s="6"/>
       <c r="H1092" s="6" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1093" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1093" s="6"/>
       <c r="B1093" s="6" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="C1093" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1093" s="6" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="E1093" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1093" s="7" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G1093" s="6"/>
       <c r="H1093" s="6" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1094" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1094" s="6"/>
       <c r="B1094" s="6" t="s">
-        <v>52</v>
+        <v>552</v>
       </c>
       <c r="C1094" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1094" s="6" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E1094" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1094" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1094" s="6"/>
       <c r="H1094" s="6" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1095" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1095" s="6"/>
       <c r="B1095" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C1095" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1095" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="E1095" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1095" s="7" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="G1095" s="6"/>
       <c r="H1095" s="6" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1096" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1096" s="6"/>
       <c r="B1096" s="6" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C1096" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1096" s="6" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E1096" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1096" s="7" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="G1096" s="6"/>
-      <c r="H1096" s="6"/>
+      <c r="H1096" s="6" t="s">
+        <v>1551</v>
+      </c>
     </row>
     <row r="1097" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1097" s="6"/>
       <c r="B1097" s="6" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C1097" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1097" s="6" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E1097" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1097" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G1097" s="6"/>
       <c r="H1097" s="6" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1098" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1098" s="6"/>
       <c r="B1098" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1098" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1098" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E1098" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1098" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G1098" s="6"/>
-      <c r="H1098" s="6" t="s">
-        <v>1552</v>
-      </c>
+      <c r="H1098" s="6"/>
     </row>
     <row r="1099" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1099" s="6"/>
       <c r="B1099" s="6" t="s">
-        <v>415</v>
+        <v>66</v>
       </c>
       <c r="C1099" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1099" s="6" t="s">
-        <v>415</v>
+        <v>66</v>
       </c>
       <c r="E1099" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1099" s="7" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G1099" s="6"/>
       <c r="H1099" s="6" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1100" s="6"/>
       <c r="B1100" s="6" t="s">
-        <v>415</v>
+        <v>66</v>
       </c>
       <c r="C1100" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1100" s="6" t="s">
-        <v>417</v>
+        <v>67</v>
       </c>
       <c r="E1100" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1100" s="7" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G1100" s="6"/>
       <c r="H1100" s="6" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1101" s="6"/>
       <c r="B1101" s="6" t="s">
-        <v>1554</v>
+        <v>415</v>
       </c>
       <c r="C1101" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1101" s="6" t="s">
-        <v>1555</v>
+        <v>415</v>
       </c>
       <c r="E1101" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1101" s="7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G1101" s="6"/>
       <c r="H1101" s="6" t="s">
-        <v>1556</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1102" s="6"/>
       <c r="B1102" s="6" t="s">
-        <v>70</v>
+        <v>415</v>
       </c>
       <c r="C1102" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1102" s="6" t="s">
-        <v>71</v>
+        <v>417</v>
       </c>
       <c r="E1102" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1102" s="12" t="s">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="F1102" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="G1102" s="6"/>
       <c r="H1102" s="6" t="s">
-        <v>1557</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1103" s="6"/>
       <c r="B1103" s="6" t="s">
-        <v>715</v>
+        <v>1554</v>
       </c>
       <c r="C1103" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1103" s="6" t="s">
-        <v>716</v>
+        <v>1555</v>
       </c>
       <c r="E1103" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1103" s="7" t="s">
-        <v>885</v>
+        <v>26</v>
       </c>
       <c r="G1103" s="6"/>
       <c r="H1103" s="6" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1104" s="6"/>
       <c r="B1104" s="6" t="s">
-        <v>1558</v>
+        <v>70</v>
       </c>
       <c r="C1104" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1104" s="6" t="s">
-        <v>1559</v>
+        <v>71</v>
       </c>
       <c r="E1104" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1104" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="F1104" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="G1104" s="6"/>
       <c r="H1104" s="6" t="s">
-        <v>1560</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1105" s="6"/>
       <c r="B1105" s="6" t="s">
-        <v>91</v>
+        <v>715</v>
       </c>
       <c r="C1105" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1105" s="6" t="s">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="E1105" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1105" s="7" t="s">
-        <v>92</v>
+        <v>885</v>
       </c>
       <c r="G1105" s="6"/>
       <c r="H1105" s="6" t="s">
-        <v>1561</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1106" s="6"/>
       <c r="B1106" s="6" t="s">
-        <v>271</v>
+        <v>1558</v>
       </c>
       <c r="C1106" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1106" s="6" t="s">
-        <v>271</v>
+        <v>1559</v>
       </c>
       <c r="E1106" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1106" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1106" s="6"/>
       <c r="H1106" s="6" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1107" s="6"/>
       <c r="B1107" s="6" t="s">
-        <v>271</v>
+        <v>91</v>
       </c>
       <c r="C1107" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1107" s="6" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="E1107" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1107" s="7" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="G1107" s="6"/>
       <c r="H1107" s="6" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1108" s="6"/>
       <c r="B1108" s="6" t="s">
-        <v>1563</v>
+        <v>271</v>
       </c>
       <c r="C1108" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1108" s="6" t="s">
-        <v>1564</v>
+        <v>271</v>
       </c>
       <c r="E1108" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1108" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1108" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="G1108" s="6"/>
       <c r="H1108" s="6" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1109" s="6"/>
       <c r="B1109" s="6" t="s">
-        <v>1566</v>
+        <v>271</v>
       </c>
       <c r="C1109" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1109" s="6" t="s">
-        <v>1566</v>
+        <v>273</v>
       </c>
       <c r="E1109" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1109" s="7" t="s">
-        <v>614</v>
+        <v>56</v>
       </c>
       <c r="G1109" s="6"/>
       <c r="H1109" s="6" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1110" s="6"/>
       <c r="B1110" s="6" t="s">
-        <v>193</v>
+        <v>1563</v>
       </c>
       <c r="C1110" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1110" s="6" t="s">
-        <v>194</v>
+        <v>1564</v>
       </c>
       <c r="E1110" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1110" s="7" t="s">
-        <v>60</v>
+        <v>31</v>
+      </c>
+      <c r="F1110" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1110" s="6"/>
       <c r="H1110" s="6" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1111" s="6"/>
       <c r="B1111" s="6" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="C1111" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1111" s="6" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="E1111" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1111" s="7" t="s">
-        <v>35</v>
+        <v>614</v>
       </c>
       <c r="G1111" s="6"/>
       <c r="H1111" s="6" t="s">
-        <v>1570</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1112" s="6"/>
       <c r="B1112" s="6" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="C1112" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1112" s="6" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="E1112" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1112" s="7" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G1112" s="6"/>
       <c r="H1112" s="6" t="s">
-        <v>431</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1113" s="6"/>
       <c r="B1113" s="6" t="s">
-        <v>108</v>
+        <v>1569</v>
       </c>
       <c r="C1113" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1113" s="6" t="s">
-        <v>108</v>
+        <v>1569</v>
       </c>
       <c r="E1113" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1113" s="7" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="G1113" s="6"/>
       <c r="H1113" s="6" t="s">
-        <v>1561</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1114" s="6"/>
       <c r="B1114" s="6" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="C1114" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1114" s="6" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="E1114" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1114" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G1114" s="6"/>
       <c r="H1114" s="6" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1115" s="6"/>
+      <c r="B1115" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1115" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1115" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1115" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1115" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1115" s="6"/>
+      <c r="H1115" s="6" t="s">
         <v>1561</v>
       </c>
     </row>
-    <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1115" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1116" s="6"/>
       <c r="B1116" s="6" t="s">
-        <v>1572</v>
+        <v>108</v>
       </c>
       <c r="C1116" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1116" s="6" t="s">
-        <v>987</v>
+        <v>109</v>
       </c>
       <c r="E1116" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1116" s="7" t="s">
-        <v>1573</v>
+        <v>56</v>
       </c>
       <c r="G1116" s="6"/>
       <c r="H1116" s="6" t="s">
-        <v>1574</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1117" s="6"/>
-      <c r="B1117" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="C1117" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1117" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="E1117" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1117" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1117" s="6"/>
-      <c r="H1117" s="6" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1117" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1118" s="6"/>
       <c r="B1118" s="6" t="s">
-        <v>961</v>
+        <v>1572</v>
       </c>
       <c r="C1118" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1118" s="6" t="s">
-        <v>962</v>
+        <v>987</v>
       </c>
       <c r="E1118" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1118" s="7" t="s">
-        <v>98</v>
+        <v>1573</v>
       </c>
       <c r="G1118" s="6"/>
       <c r="H1118" s="6" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1119" s="6"/>
       <c r="B1119" s="6" t="s">
-        <v>127</v>
+        <v>959</v>
       </c>
       <c r="C1119" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1119" s="6" t="s">
-        <v>127</v>
+        <v>959</v>
       </c>
       <c r="E1119" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1119" s="7" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="G1119" s="6"/>
       <c r="H1119" s="6" t="s">
-        <v>996</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1120" s="6"/>
       <c r="B1120" s="6" t="s">
-        <v>129</v>
+        <v>961</v>
       </c>
       <c r="C1120" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1120" s="6" t="s">
-        <v>130</v>
+        <v>962</v>
       </c>
       <c r="E1120" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1120" s="7" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="G1120" s="6"/>
       <c r="H1120" s="6" t="s">
-        <v>996</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1121" s="6"/>
       <c r="B1121" s="6" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="C1121" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1121" s="6" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="E1121" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1121" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G1121" s="6"/>
       <c r="H1121" s="6" t="s">
-        <v>1576</v>
+        <v>996</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1122" s="6"/>
       <c r="B1122" s="6" t="s">
-        <v>1577</v>
+        <v>129</v>
       </c>
       <c r="C1122" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1122" s="6" t="s">
-        <v>1577</v>
+        <v>130</v>
       </c>
       <c r="E1122" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1122" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G1122" s="6"/>
       <c r="H1122" s="6" t="s">
-        <v>1578</v>
+        <v>996</v>
       </c>
     </row>
     <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1123" s="6"/>
       <c r="B1123" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C1123" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1123" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E1123" s="6" t="s">
         <v>19</v>
@@ -36411,41 +36415,41 @@
       </c>
       <c r="G1123" s="6"/>
       <c r="H1123" s="6" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1124" s="6"/>
       <c r="B1124" s="6" t="s">
-        <v>325</v>
+        <v>1577</v>
       </c>
       <c r="C1124" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1124" s="6" t="s">
-        <v>326</v>
+        <v>1577</v>
       </c>
       <c r="E1124" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1124" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1124" s="6"/>
       <c r="H1124" s="6" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1125" s="6"/>
       <c r="B1125" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1125" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1125" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E1125" s="6" t="s">
         <v>19</v>
@@ -36455,63 +36459,63 @@
       </c>
       <c r="G1125" s="6"/>
       <c r="H1125" s="6" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1126" s="6"/>
       <c r="B1126" s="6" t="s">
-        <v>39</v>
+        <v>325</v>
       </c>
       <c r="C1126" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1126" s="6" t="s">
-        <v>41</v>
+        <v>326</v>
       </c>
       <c r="E1126" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1126" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G1126" s="6"/>
       <c r="H1126" s="6" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1127" s="6"/>
       <c r="B1127" s="6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C1127" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1127" s="6" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E1127" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1127" s="7" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="G1127" s="6"/>
       <c r="H1127" s="6" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1128" s="6"/>
       <c r="B1128" s="6" t="s">
-        <v>1583</v>
+        <v>39</v>
       </c>
       <c r="C1128" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1128" s="6" t="s">
-        <v>1583</v>
+        <v>41</v>
       </c>
       <c r="E1128" s="6" t="s">
         <v>19</v>
@@ -36521,25 +36525,25 @@
       </c>
       <c r="G1128" s="6"/>
       <c r="H1128" s="6" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1129" s="6"/>
       <c r="B1129" s="6" t="s">
-        <v>1584</v>
+        <v>48</v>
       </c>
       <c r="C1129" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1129" s="6" t="s">
-        <v>1584</v>
+        <v>50</v>
       </c>
       <c r="E1129" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1129" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1129" s="6"/>
       <c r="H1129" s="6" t="s">
@@ -36549,35 +36553,35 @@
     <row r="1130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1130" s="6"/>
       <c r="B1130" s="6" t="s">
-        <v>964</v>
+        <v>1583</v>
       </c>
       <c r="C1130" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1130" s="6" t="s">
-        <v>965</v>
+        <v>1583</v>
       </c>
       <c r="E1130" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1130" s="7" t="s">
-        <v>452</v>
+        <v>35</v>
       </c>
       <c r="G1130" s="6"/>
       <c r="H1130" s="6" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1131" s="6"/>
       <c r="B1131" s="6" t="s">
-        <v>52</v>
+        <v>1584</v>
       </c>
       <c r="C1131" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1131" s="6" t="s">
-        <v>52</v>
+        <v>1584</v>
       </c>
       <c r="E1131" s="6" t="s">
         <v>19</v>
@@ -36587,177 +36591,177 @@
       </c>
       <c r="G1131" s="6"/>
       <c r="H1131" s="6" t="s">
-        <v>1586</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1132" s="6"/>
       <c r="B1132" s="6" t="s">
-        <v>52</v>
+        <v>964</v>
       </c>
       <c r="C1132" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1132" s="6" t="s">
-        <v>55</v>
+        <v>965</v>
       </c>
       <c r="E1132" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1132" s="7" t="s">
-        <v>56</v>
+        <v>452</v>
       </c>
       <c r="G1132" s="6"/>
       <c r="H1132" s="6" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1133" s="6"/>
       <c r="B1133" s="6" t="s">
-        <v>394</v>
+        <v>52</v>
       </c>
       <c r="C1133" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1133" s="6" t="s">
-        <v>396</v>
+        <v>52</v>
       </c>
       <c r="E1133" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1133" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G1133" s="6"/>
       <c r="H1133" s="6" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1134" s="6"/>
       <c r="B1134" s="6" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C1134" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1134" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E1134" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1134" s="7" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="G1134" s="6"/>
-      <c r="H1134" s="6"/>
+      <c r="H1134" s="6" t="s">
+        <v>1587</v>
+      </c>
     </row>
     <row r="1135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1135" s="6"/>
       <c r="B1135" s="6" t="s">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="C1135" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1135" s="6" t="s">
-        <v>66</v>
+        <v>396</v>
       </c>
       <c r="E1135" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1135" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G1135" s="6"/>
       <c r="H1135" s="6" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1136" s="6"/>
       <c r="B1136" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C1136" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1136" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E1136" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1136" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G1136" s="6"/>
-      <c r="H1136" s="6" t="s">
-        <v>1589</v>
-      </c>
+      <c r="H1136" s="6"/>
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1137" s="6"/>
       <c r="B1137" s="6" t="s">
-        <v>778</v>
+        <v>66</v>
       </c>
       <c r="C1137" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1137" s="6" t="s">
-        <v>778</v>
+        <v>66</v>
       </c>
       <c r="E1137" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1137" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G1137" s="6"/>
       <c r="H1137" s="6" t="s">
-        <v>779</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1138" s="6"/>
       <c r="B1138" s="6" t="s">
-        <v>780</v>
+        <v>66</v>
       </c>
       <c r="C1138" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1138" s="6" t="s">
-        <v>780</v>
+        <v>67</v>
       </c>
       <c r="E1138" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1138" s="7" t="s">
-        <v>366</v>
+        <v>67</v>
       </c>
       <c r="G1138" s="6"/>
       <c r="H1138" s="6" t="s">
-        <v>781</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1139" s="6"/>
       <c r="B1139" s="6" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C1139" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1139" s="6" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="E1139" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1139" s="7" t="s">
-        <v>784</v>
+        <v>53</v>
       </c>
       <c r="G1139" s="6"/>
       <c r="H1139" s="6" t="s">
@@ -36767,13 +36771,13 @@
     <row r="1140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1140" s="6"/>
       <c r="B1140" s="6" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C1140" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1140" s="6" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="E1140" s="6" t="s">
         <v>19</v>
@@ -36789,211 +36793,211 @@
     <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1141" s="6"/>
       <c r="B1141" s="6" t="s">
-        <v>1008</v>
+        <v>782</v>
       </c>
       <c r="C1141" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1141" s="6" t="s">
-        <v>1010</v>
+        <v>783</v>
       </c>
       <c r="E1141" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1141" s="7" t="s">
-        <v>56</v>
+        <v>784</v>
       </c>
       <c r="G1141" s="6"/>
       <c r="H1141" s="6" t="s">
-        <v>1009</v>
+        <v>779</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1142" s="6"/>
       <c r="B1142" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C1142" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1142" s="6" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E1142" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1142" s="7" t="s">
-        <v>48</v>
+        <v>366</v>
       </c>
       <c r="G1142" s="6"/>
       <c r="H1142" s="6" t="s">
-        <v>1590</v>
+        <v>781</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1143" s="6"/>
       <c r="B1143" s="6" t="s">
-        <v>787</v>
+        <v>1008</v>
       </c>
       <c r="C1143" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1143" s="6" t="s">
-        <v>789</v>
+        <v>1010</v>
       </c>
       <c r="E1143" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1143" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G1143" s="6"/>
       <c r="H1143" s="6" t="s">
-        <v>1590</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="1144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1144" s="6"/>
       <c r="B1144" s="6" t="s">
-        <v>166</v>
+        <v>787</v>
       </c>
       <c r="C1144" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1144" s="6" t="s">
-        <v>168</v>
+        <v>787</v>
       </c>
       <c r="E1144" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1144" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G1144" s="6"/>
       <c r="H1144" s="6" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1145" s="6"/>
       <c r="B1145" s="6" t="s">
-        <v>70</v>
+        <v>787</v>
       </c>
       <c r="C1145" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1145" s="6" t="s">
-        <v>71</v>
+        <v>789</v>
       </c>
       <c r="E1145" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1145" s="12" t="s">
-        <v>72</v>
+        <v>19</v>
+      </c>
+      <c r="F1145" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="G1145" s="6"/>
       <c r="H1145" s="6" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1146" s="6"/>
       <c r="B1146" s="6" t="s">
-        <v>839</v>
+        <v>166</v>
       </c>
       <c r="C1146" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1146" s="6" t="s">
-        <v>839</v>
+        <v>168</v>
       </c>
       <c r="E1146" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1146" s="7" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="G1146" s="6"/>
       <c r="H1146" s="6" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="1147" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1147" s="6"/>
       <c r="B1147" s="6" t="s">
-        <v>715</v>
+        <v>70</v>
       </c>
       <c r="C1147" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1147" s="6" t="s">
-        <v>716</v>
+        <v>71</v>
       </c>
       <c r="E1147" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1147" s="7" t="s">
-        <v>717</v>
+        <v>31</v>
+      </c>
+      <c r="F1147" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="G1147" s="6"/>
       <c r="H1147" s="6" t="s">
-        <v>1004</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1148" s="6"/>
       <c r="B1148" s="6" t="s">
-        <v>1593</v>
+        <v>839</v>
       </c>
       <c r="C1148" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1148" s="6" t="s">
-        <v>1594</v>
+        <v>839</v>
       </c>
       <c r="E1148" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1148" s="12" t="s">
-        <v>85</v>
+        <v>19</v>
+      </c>
+      <c r="F1148" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="G1148" s="6"/>
       <c r="H1148" s="6" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1149" s="6"/>
       <c r="B1149" s="6" t="s">
-        <v>91</v>
+        <v>715</v>
       </c>
       <c r="C1149" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1149" s="6" t="s">
-        <v>91</v>
+        <v>716</v>
       </c>
       <c r="E1149" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1149" s="7" t="s">
-        <v>92</v>
+        <v>717</v>
       </c>
       <c r="G1149" s="6"/>
       <c r="H1149" s="6" t="s">
-        <v>1526</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1150" s="6"/>
       <c r="B1150" s="6" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="C1150" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1150" s="6" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
       <c r="E1150" s="6" t="s">
         <v>31</v>
@@ -37003,239 +37007,239 @@
       </c>
       <c r="G1150" s="6"/>
       <c r="H1150" s="6" t="s">
-        <v>1598</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1151" s="6"/>
       <c r="B1151" s="6" t="s">
-        <v>271</v>
+        <v>91</v>
       </c>
       <c r="C1151" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1151" s="6" t="s">
-        <v>271</v>
+        <v>91</v>
       </c>
       <c r="E1151" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1151" s="7" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="G1151" s="6"/>
       <c r="H1151" s="6" t="s">
-        <v>1599</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1152" s="6"/>
       <c r="B1152" s="6" t="s">
-        <v>271</v>
+        <v>1596</v>
       </c>
       <c r="C1152" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1152" s="6" t="s">
-        <v>273</v>
+        <v>1597</v>
       </c>
       <c r="E1152" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1152" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="F1152" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="G1152" s="6"/>
       <c r="H1152" s="6" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1153" s="6"/>
       <c r="B1153" s="6" t="s">
-        <v>1600</v>
+        <v>271</v>
       </c>
       <c r="C1153" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1153" s="6" t="s">
-        <v>1600</v>
+        <v>271</v>
       </c>
       <c r="E1153" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1153" s="7" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="G1153" s="6"/>
       <c r="H1153" s="6" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1154" s="6"/>
       <c r="B1154" s="6" t="s">
-        <v>1449</v>
+        <v>271</v>
       </c>
       <c r="C1154" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1154" s="6" t="s">
-        <v>1450</v>
+        <v>273</v>
       </c>
       <c r="E1154" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1154" s="7" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="G1154" s="6"/>
       <c r="H1154" s="6" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1155" s="6"/>
       <c r="B1155" s="6" t="s">
-        <v>190</v>
+        <v>1600</v>
       </c>
       <c r="C1155" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1155" s="6" t="s">
-        <v>190</v>
+        <v>1600</v>
       </c>
       <c r="E1155" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1155" s="7" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G1155" s="6"/>
       <c r="H1155" s="6" t="s">
-        <v>940</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1156" s="6"/>
       <c r="B1156" s="6" t="s">
-        <v>190</v>
+        <v>1449</v>
       </c>
       <c r="C1156" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1156" s="6" t="s">
-        <v>191</v>
+        <v>1450</v>
       </c>
       <c r="E1156" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1156" s="7" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="G1156" s="6"/>
       <c r="H1156" s="6" t="s">
-        <v>940</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1157" s="6"/>
       <c r="B1157" s="6" t="s">
-        <v>1602</v>
+        <v>190</v>
       </c>
       <c r="C1157" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1157" s="6" t="s">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="E1157" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1157" s="7" t="s">
-        <v>1603</v>
+        <v>48</v>
       </c>
       <c r="G1157" s="6"/>
       <c r="H1157" s="6" t="s">
-        <v>1604</v>
+        <v>940</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1158" s="6"/>
       <c r="B1158" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C1158" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1158" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E1158" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1158" s="7" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G1158" s="6"/>
       <c r="H1158" s="6" t="s">
-        <v>1605</v>
+        <v>940</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1159" s="6"/>
       <c r="B1159" s="6" t="s">
-        <v>1026</v>
+        <v>1602</v>
       </c>
       <c r="C1159" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1159" s="6" t="s">
-        <v>1027</v>
+        <v>242</v>
       </c>
       <c r="E1159" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1159" s="7" t="s">
-        <v>56</v>
+        <v>1603</v>
       </c>
       <c r="G1159" s="6"/>
       <c r="H1159" s="6" t="s">
-        <v>1028</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1160" s="6"/>
       <c r="B1160" s="6" t="s">
-        <v>793</v>
+        <v>193</v>
       </c>
       <c r="C1160" s="6" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D1160" s="6" t="s">
-        <v>793</v>
+        <v>194</v>
       </c>
       <c r="E1160" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1160" s="7" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1160" s="6"/>
       <c r="H1160" s="6" t="s">
-        <v>1029</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1161" s="6"/>
       <c r="B1161" s="6" t="s">
-        <v>793</v>
+        <v>1026</v>
       </c>
       <c r="C1161" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1161" s="6" t="s">
-        <v>795</v>
+        <v>1027</v>
       </c>
       <c r="E1161" s="6" t="s">
         <v>19</v>
@@ -37245,19 +37249,19 @@
       </c>
       <c r="G1161" s="6"/>
       <c r="H1161" s="6" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1162" s="6"/>
       <c r="B1162" s="6" t="s">
-        <v>982</v>
+        <v>793</v>
       </c>
       <c r="C1162" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1162" s="6" t="s">
-        <v>982</v>
+        <v>793</v>
       </c>
       <c r="E1162" s="6" t="s">
         <v>19</v>
@@ -37267,19 +37271,19 @@
       </c>
       <c r="G1162" s="6"/>
       <c r="H1162" s="6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1163" s="6"/>
       <c r="B1163" s="6" t="s">
-        <v>982</v>
+        <v>793</v>
       </c>
       <c r="C1163" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1163" s="6" t="s">
-        <v>984</v>
+        <v>795</v>
       </c>
       <c r="E1163" s="6" t="s">
         <v>19</v>
@@ -37289,204 +37293,248 @@
       </c>
       <c r="G1163" s="6"/>
       <c r="H1163" s="6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1164" s="6"/>
       <c r="B1164" s="6" t="s">
-        <v>1606</v>
+        <v>982</v>
       </c>
       <c r="C1164" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1164" s="6" t="s">
-        <v>1606</v>
+        <v>982</v>
       </c>
       <c r="E1164" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1164" s="7" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G1164" s="6"/>
       <c r="H1164" s="6" t="s">
-        <v>1607</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1165" s="6"/>
       <c r="B1165" s="6" t="s">
-        <v>1606</v>
+        <v>982</v>
       </c>
       <c r="C1165" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1165" s="6" t="s">
-        <v>1608</v>
+        <v>984</v>
       </c>
       <c r="E1165" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1165" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="G1165" s="6"/>
       <c r="H1165" s="6" t="s">
-        <v>1607</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1166" s="6"/>
       <c r="B1166" s="6" t="s">
-        <v>427</v>
+        <v>1606</v>
       </c>
       <c r="C1166" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1166" s="6" t="s">
-        <v>427</v>
+        <v>1606</v>
       </c>
       <c r="E1166" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1166" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G1166" s="6"/>
       <c r="H1166" s="6" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1167" s="6"/>
       <c r="B1167" s="6" t="s">
-        <v>427</v>
+        <v>1606</v>
       </c>
       <c r="C1167" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1167" s="6" t="s">
-        <v>429</v>
+        <v>1608</v>
       </c>
       <c r="E1167" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1167" s="7" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G1167" s="6"/>
       <c r="H1167" s="6" t="s">
-        <v>1610</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1168" s="6"/>
       <c r="B1168" s="6" t="s">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="C1168" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1168" s="6" t="s">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="E1168" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1168" s="7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G1168" s="6"/>
       <c r="H1168" s="6" t="s">
-        <v>796</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1169" s="6"/>
       <c r="B1169" s="6" t="s">
-        <v>215</v>
+        <v>427</v>
       </c>
       <c r="C1169" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1169" s="6" t="s">
-        <v>217</v>
+        <v>429</v>
       </c>
       <c r="E1169" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1169" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G1169" s="6"/>
       <c r="H1169" s="6" t="s">
-        <v>796</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1170" s="6"/>
       <c r="B1170" s="6" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="C1170" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D1170" s="6" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="E1170" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1170" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G1170" s="6"/>
       <c r="H1170" s="6" t="s">
-        <v>1537</v>
+        <v>796</v>
       </c>
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1171" s="6"/>
       <c r="B1171" s="6" t="s">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="C1171" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D1171" s="6" t="s">
-        <v>109</v>
+        <v>217</v>
       </c>
       <c r="E1171" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1171" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G1171" s="6"/>
       <c r="H1171" s="6" t="s">
-        <v>1611</v>
+        <v>796</v>
       </c>
     </row>
     <row r="1172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1172" s="6"/>
       <c r="B1172" s="6" t="s">
-        <v>743</v>
+        <v>108</v>
       </c>
       <c r="C1172" s="6" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D1172" s="6" t="s">
-        <v>744</v>
+        <v>108</v>
       </c>
       <c r="E1172" s="6" t="s">
         <v>19</v>
       </c>
       <c r="F1172" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G1172" s="6"/>
       <c r="H1172" s="6" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1173" s="6"/>
+      <c r="B1173" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1173" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1173" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1173" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1173" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1173" s="6"/>
+      <c r="H1173" s="6" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1174" s="6"/>
+      <c r="B1174" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="C1174" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1174" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="E1174" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1174" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1174" s="6"/>
+      <c r="H1174" s="6" t="s">
         <v>1034</v>
       </c>
     </row>
